--- a/assets/constructions/examples/ctd_inserts_grooving.xlsx
+++ b/assets/constructions/examples/ctd_inserts_grooving.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX6"/>
+  <dimension ref="A1:BC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -679,11 +679,36 @@
           <t>adintws</t>
         </is>
       </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QD-NG-0300-035M-PH  4240</t>
+          <t>N123T3-0300-RS      1125</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -693,14 +718,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PMK</t>
+          <t>PMKNS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SAND_QD-03</t>
+          <t>SAND_N123T3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -710,27 +735,27 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CoroMill QD -size G</t>
+          <t>CoroCut 3 -style T</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CoroMillⓇ QD insert for grooving</t>
+          <t>CoroCutⓇ 3 insert for profiling</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>QD-NG-0300</t>
+          <t>N123T3-0300</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -742,51 +767,53 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>QD-NG-0300</t>
+          <t>N123T3-0300</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>6</v>
+      </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W2" t="n">
         <v>3</v>
       </c>
       <c r="X2" t="n">
-        <v>0.005</v>
+        <v>-0.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.105</v>
+        <v>0.02</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
         <v>7</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.05</v>
+      </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr">
         <is>
@@ -796,7 +823,7 @@
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="n">
-        <v>0.003</v>
+        <v>0.012</v>
       </c>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
@@ -816,7 +843,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>CVD</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
@@ -825,58 +852,77 @@
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>COR_QD-030</t>
+          <t>COR_N123T3</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AY2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MRMN500-M-2120</t>
+          <t>QD-NE-0200-020E-PL  4340</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LIKON</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>PMK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LIK_MG/R500W</t>
+          <t>SAND_QD-02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>LIKON</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>CoroMill QD -size E</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>CoroMillⓇ QD insert for grooving</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>MRMN500</t>
+          <t>QD-NE-0200</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -888,15 +934,15 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>MRMN500-M</t>
+          <t>QD-NE-0200</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>7</v>
@@ -904,23 +950,33 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>5</v>
-      </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.055</v>
+      </c>
       <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+      <c r="AA3" t="n">
+        <v>7</v>
+      </c>
       <c r="AB3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
@@ -930,16 +986,16 @@
         </is>
       </c>
       <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="n">
-        <v>25.86</v>
-      </c>
-      <c r="AK3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="n">
+        <v>0.001</v>
+      </c>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>2022/LIKON Инструментальный каталог</t>
+          <t>2021/www.sandvik.coromant.com</t>
         </is>
       </c>
       <c r="AP3" t="n">
@@ -952,32 +1008,39 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>CVD</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>LIKON_MG/R500W</t>
+          <t>COR_QD-020</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AY3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>PMK</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QD-NL-0800-0008-TF  H13A</t>
+          <t>R123J2-0500-0504-CR 2135</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -987,14 +1050,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MKNS</t>
+          <t>PMKS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SAND_</t>
+          <t>SAND_123J2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1004,67 +1067,69 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>TF</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CoroCut QD -size L</t>
+          <t>CoroCut 1-2 -size J2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>CoroCutⓇ QD insert for turning</t>
+          <t>CoroCutⓇ 1-2 insert for parting</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>QD-NL-0800</t>
+          <t>R123J2-0500</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>H13A</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="N4" t="b">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>QD-NL-0800</t>
+          <t>R123J2-0500</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
         <v>7</v>
       </c>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>23.6</v>
+      </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
@@ -1074,27 +1139,27 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>0.02</v>
+        <v>0.008</v>
       </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
@@ -1114,7 +1179,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>CVD</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
@@ -1123,66 +1188,69 @@
       <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>COR_QD-080</t>
+          <t>COR_R123_J</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AY4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>PMKS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N151.2-200-20-5G    4225</t>
+          <t>MGMN300-G-2120</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>LIKON</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SAND_151.2-20</t>
+          <t>LIK_MG/R300W</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>LIKON</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5G</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Q-Cut 151.2 -size 20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>T-MaxⓇ Q-Cut insert for grooving</t>
-        </is>
-      </c>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>N151.2-200</t>
+          <t>MGMN300</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1194,15 +1262,15 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>N151.2-200</t>
+          <t>MGMN300-G</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
         <v>7</v>
@@ -1210,39 +1278,25 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="n">
-        <v>7</v>
-      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0.4</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1250,16 +1304,16 @@
         </is>
       </c>
       <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="AJ5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>2021/www.sandvik.coromant.com</t>
+          <t>2022/LIKON Инструментальный каталог</t>
         </is>
       </c>
       <c r="AP5" t="n">
@@ -1272,28 +1326,43 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>CVD</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
+      <c r="AU5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.2</v>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>COR_151.2-20</t>
+          <t>LIKON_MG/R300W</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AY5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QD-NF-0250-0001-CF  4325</t>
+          <t>N123U3-0100-RS      1125</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1303,14 +1372,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>PMKNS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SAND_</t>
+          <t>SAND_N123U3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1320,27 +1389,27 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CoroCut QD -size F</t>
+          <t>CoroCut 3 -style U</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>CoroCutⓇ QD insert for parting</t>
+          <t>CoroCutⓇ 3 insert for profiling</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>QD-NF-0250</t>
+          <t>N123U3-0100</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1352,49 +1421,47 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>N123U3-0100</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>11</v>
+      </c>
+      <c r="V6" t="n">
+        <v>3</v>
+      </c>
+      <c r="W6" t="n">
         <v>1</v>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>QD-NF-0250</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7</v>
-      </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.5</v>
-      </c>
       <c r="X6" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
         <v>7</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0.15</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="n">
         <v>-0.05</v>
       </c>
@@ -1410,7 +1477,7 @@
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
@@ -1430,7 +1497,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>CVD</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
@@ -1439,12 +1506,23 @@
       <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>COR_QD-025</t>
+          <t>COR_N123U3</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AY6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
